--- a/สรุปคะแนน_1สทค2.xlsx
+++ b/สรุปคะแนน_1สทค2.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="สรุปผลการเรียนและตัดเกรด" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="คะแนนดิบ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="จับคู่บัญชี-อีเมล" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="สรุปผลการเรียนและตัดเกรด" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="คะแนนดิบ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="จับคู่บัญชี-อีเมล" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -841,7 +841,7 @@
       <c r="F6" s="18" t="inlineStr">
         <is>
           <t>คะแนนดิบ
-(เต็ม 130)</t>
+(เต็ม 150)</t>
         </is>
       </c>
       <c r="G6" s="18" t="inlineStr">
@@ -914,15 +914,15 @@
         <v/>
       </c>
       <c r="F7" s="28">
-        <f>'คะแนนดิบ'!Q6</f>
+        <f>'คะแนนดิบ'!R6</f>
         <v/>
       </c>
       <c r="G7" s="27">
-        <f>ROUND((F7/130)*50, 2)</f>
+        <f>ROUND((F7/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H7" s="28">
-        <f>'คะแนนดิบ'!U6</f>
+        <f>'คะแนนดิบ'!V6</f>
         <v/>
       </c>
       <c r="I7" s="27">
@@ -930,7 +930,7 @@
         <v/>
       </c>
       <c r="J7" s="28">
-        <f>'คะแนนดิบ'!X6</f>
+        <f>'คะแนนดิบ'!Y6</f>
         <v/>
       </c>
       <c r="K7" s="27">
@@ -972,15 +972,15 @@
         <v/>
       </c>
       <c r="F8" s="36">
-        <f>'คะแนนดิบ'!Q7</f>
+        <f>'คะแนนดิบ'!R7</f>
         <v/>
       </c>
       <c r="G8" s="35">
-        <f>ROUND((F8/130)*50, 2)</f>
+        <f>ROUND((F8/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H8" s="36">
-        <f>'คะแนนดิบ'!U7</f>
+        <f>'คะแนนดิบ'!V7</f>
         <v/>
       </c>
       <c r="I8" s="35">
@@ -988,7 +988,7 @@
         <v/>
       </c>
       <c r="J8" s="36">
-        <f>'คะแนนดิบ'!X7</f>
+        <f>'คะแนนดิบ'!Y7</f>
         <v/>
       </c>
       <c r="K8" s="35">
@@ -1030,15 +1030,15 @@
         <v/>
       </c>
       <c r="F9" s="28">
-        <f>'คะแนนดิบ'!Q8</f>
+        <f>'คะแนนดิบ'!R8</f>
         <v/>
       </c>
       <c r="G9" s="27">
-        <f>ROUND((F9/130)*50, 2)</f>
+        <f>ROUND((F9/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H9" s="28">
-        <f>'คะแนนดิบ'!U8</f>
+        <f>'คะแนนดิบ'!V8</f>
         <v/>
       </c>
       <c r="I9" s="27">
@@ -1046,7 +1046,7 @@
         <v/>
       </c>
       <c r="J9" s="28">
-        <f>'คะแนนดิบ'!X8</f>
+        <f>'คะแนนดิบ'!Y8</f>
         <v/>
       </c>
       <c r="K9" s="27">
@@ -1088,15 +1088,15 @@
         <v/>
       </c>
       <c r="F10" s="36">
-        <f>'คะแนนดิบ'!Q9</f>
+        <f>'คะแนนดิบ'!R9</f>
         <v/>
       </c>
       <c r="G10" s="35">
-        <f>ROUND((F10/130)*50, 2)</f>
+        <f>ROUND((F10/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H10" s="36">
-        <f>'คะแนนดิบ'!U9</f>
+        <f>'คะแนนดิบ'!V9</f>
         <v/>
       </c>
       <c r="I10" s="35">
@@ -1104,7 +1104,7 @@
         <v/>
       </c>
       <c r="J10" s="36">
-        <f>'คะแนนดิบ'!X9</f>
+        <f>'คะแนนดิบ'!Y9</f>
         <v/>
       </c>
       <c r="K10" s="35">
@@ -1146,15 +1146,15 @@
         <v/>
       </c>
       <c r="F11" s="28">
-        <f>'คะแนนดิบ'!Q10</f>
+        <f>'คะแนนดิบ'!R10</f>
         <v/>
       </c>
       <c r="G11" s="27">
-        <f>ROUND((F11/130)*50, 2)</f>
+        <f>ROUND((F11/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H11" s="28">
-        <f>'คะแนนดิบ'!U10</f>
+        <f>'คะแนนดิบ'!V10</f>
         <v/>
       </c>
       <c r="I11" s="27">
@@ -1162,7 +1162,7 @@
         <v/>
       </c>
       <c r="J11" s="28">
-        <f>'คะแนนดิบ'!X10</f>
+        <f>'คะแนนดิบ'!Y10</f>
         <v/>
       </c>
       <c r="K11" s="27">
@@ -1204,15 +1204,15 @@
         <v/>
       </c>
       <c r="F12" s="36">
-        <f>'คะแนนดิบ'!Q11</f>
+        <f>'คะแนนดิบ'!R11</f>
         <v/>
       </c>
       <c r="G12" s="35">
-        <f>ROUND((F12/130)*50, 2)</f>
+        <f>ROUND((F12/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H12" s="36">
-        <f>'คะแนนดิบ'!U11</f>
+        <f>'คะแนนดิบ'!V11</f>
         <v/>
       </c>
       <c r="I12" s="35">
@@ -1220,7 +1220,7 @@
         <v/>
       </c>
       <c r="J12" s="36">
-        <f>'คะแนนดิบ'!X11</f>
+        <f>'คะแนนดิบ'!Y11</f>
         <v/>
       </c>
       <c r="K12" s="35">
@@ -1262,15 +1262,15 @@
         <v/>
       </c>
       <c r="F13" s="28">
-        <f>'คะแนนดิบ'!Q12</f>
+        <f>'คะแนนดิบ'!R12</f>
         <v/>
       </c>
       <c r="G13" s="27">
-        <f>ROUND((F13/130)*50, 2)</f>
+        <f>ROUND((F13/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H13" s="28">
-        <f>'คะแนนดิบ'!U12</f>
+        <f>'คะแนนดิบ'!V12</f>
         <v/>
       </c>
       <c r="I13" s="27">
@@ -1278,7 +1278,7 @@
         <v/>
       </c>
       <c r="J13" s="28">
-        <f>'คะแนนดิบ'!X12</f>
+        <f>'คะแนนดิบ'!Y12</f>
         <v/>
       </c>
       <c r="K13" s="27">
@@ -1320,15 +1320,15 @@
         <v/>
       </c>
       <c r="F14" s="36">
-        <f>'คะแนนดิบ'!Q13</f>
+        <f>'คะแนนดิบ'!R13</f>
         <v/>
       </c>
       <c r="G14" s="35">
-        <f>ROUND((F14/130)*50, 2)</f>
+        <f>ROUND((F14/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H14" s="36">
-        <f>'คะแนนดิบ'!U13</f>
+        <f>'คะแนนดิบ'!V13</f>
         <v/>
       </c>
       <c r="I14" s="35">
@@ -1336,7 +1336,7 @@
         <v/>
       </c>
       <c r="J14" s="36">
-        <f>'คะแนนดิบ'!X13</f>
+        <f>'คะแนนดิบ'!Y13</f>
         <v/>
       </c>
       <c r="K14" s="35">
@@ -1378,15 +1378,15 @@
         <v/>
       </c>
       <c r="F15" s="28">
-        <f>'คะแนนดิบ'!Q14</f>
+        <f>'คะแนนดิบ'!R14</f>
         <v/>
       </c>
       <c r="G15" s="27">
-        <f>ROUND((F15/130)*50, 2)</f>
+        <f>ROUND((F15/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H15" s="28">
-        <f>'คะแนนดิบ'!U14</f>
+        <f>'คะแนนดิบ'!V14</f>
         <v/>
       </c>
       <c r="I15" s="27">
@@ -1394,7 +1394,7 @@
         <v/>
       </c>
       <c r="J15" s="28">
-        <f>'คะแนนดิบ'!X14</f>
+        <f>'คะแนนดิบ'!Y14</f>
         <v/>
       </c>
       <c r="K15" s="27">
@@ -1436,15 +1436,15 @@
         <v/>
       </c>
       <c r="F16" s="36">
-        <f>'คะแนนดิบ'!Q15</f>
+        <f>'คะแนนดิบ'!R15</f>
         <v/>
       </c>
       <c r="G16" s="35">
-        <f>ROUND((F16/130)*50, 2)</f>
+        <f>ROUND((F16/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H16" s="36">
-        <f>'คะแนนดิบ'!U15</f>
+        <f>'คะแนนดิบ'!V15</f>
         <v/>
       </c>
       <c r="I16" s="35">
@@ -1452,7 +1452,7 @@
         <v/>
       </c>
       <c r="J16" s="36">
-        <f>'คะแนนดิบ'!X15</f>
+        <f>'คะแนนดิบ'!Y15</f>
         <v/>
       </c>
       <c r="K16" s="35">
@@ -1494,15 +1494,15 @@
         <v/>
       </c>
       <c r="F17" s="28">
-        <f>'คะแนนดิบ'!Q16</f>
+        <f>'คะแนนดิบ'!R16</f>
         <v/>
       </c>
       <c r="G17" s="27">
-        <f>ROUND((F17/130)*50, 2)</f>
+        <f>ROUND((F17/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H17" s="28">
-        <f>'คะแนนดิบ'!U16</f>
+        <f>'คะแนนดิบ'!V16</f>
         <v/>
       </c>
       <c r="I17" s="27">
@@ -1510,7 +1510,7 @@
         <v/>
       </c>
       <c r="J17" s="28">
-        <f>'คะแนนดิบ'!X16</f>
+        <f>'คะแนนดิบ'!Y16</f>
         <v/>
       </c>
       <c r="K17" s="27">
@@ -1552,15 +1552,15 @@
         <v/>
       </c>
       <c r="F18" s="36">
-        <f>'คะแนนดิบ'!Q17</f>
+        <f>'คะแนนดิบ'!R17</f>
         <v/>
       </c>
       <c r="G18" s="35">
-        <f>ROUND((F18/130)*50, 2)</f>
+        <f>ROUND((F18/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H18" s="36">
-        <f>'คะแนนดิบ'!U17</f>
+        <f>'คะแนนดิบ'!V17</f>
         <v/>
       </c>
       <c r="I18" s="35">
@@ -1568,7 +1568,7 @@
         <v/>
       </c>
       <c r="J18" s="36">
-        <f>'คะแนนดิบ'!X17</f>
+        <f>'คะแนนดิบ'!Y17</f>
         <v/>
       </c>
       <c r="K18" s="35">
@@ -1610,15 +1610,15 @@
         <v/>
       </c>
       <c r="F19" s="28">
-        <f>'คะแนนดิบ'!Q18</f>
+        <f>'คะแนนดิบ'!R18</f>
         <v/>
       </c>
       <c r="G19" s="27">
-        <f>ROUND((F19/130)*50, 2)</f>
+        <f>ROUND((F19/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H19" s="28">
-        <f>'คะแนนดิบ'!U18</f>
+        <f>'คะแนนดิบ'!V18</f>
         <v/>
       </c>
       <c r="I19" s="27">
@@ -1626,7 +1626,7 @@
         <v/>
       </c>
       <c r="J19" s="28">
-        <f>'คะแนนดิบ'!X18</f>
+        <f>'คะแนนดิบ'!Y18</f>
         <v/>
       </c>
       <c r="K19" s="27">
@@ -1668,15 +1668,15 @@
         <v/>
       </c>
       <c r="F20" s="36">
-        <f>'คะแนนดิบ'!Q19</f>
+        <f>'คะแนนดิบ'!R19</f>
         <v/>
       </c>
       <c r="G20" s="35">
-        <f>ROUND((F20/130)*50, 2)</f>
+        <f>ROUND((F20/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H20" s="36">
-        <f>'คะแนนดิบ'!U19</f>
+        <f>'คะแนนดิบ'!V19</f>
         <v/>
       </c>
       <c r="I20" s="35">
@@ -1684,7 +1684,7 @@
         <v/>
       </c>
       <c r="J20" s="36">
-        <f>'คะแนนดิบ'!X19</f>
+        <f>'คะแนนดิบ'!Y19</f>
         <v/>
       </c>
       <c r="K20" s="35">
@@ -1726,15 +1726,15 @@
         <v/>
       </c>
       <c r="F21" s="28">
-        <f>'คะแนนดิบ'!Q20</f>
+        <f>'คะแนนดิบ'!R20</f>
         <v/>
       </c>
       <c r="G21" s="27">
-        <f>ROUND((F21/130)*50, 2)</f>
+        <f>ROUND((F21/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H21" s="28">
-        <f>'คะแนนดิบ'!U20</f>
+        <f>'คะแนนดิบ'!V20</f>
         <v/>
       </c>
       <c r="I21" s="27">
@@ -1742,7 +1742,7 @@
         <v/>
       </c>
       <c r="J21" s="28">
-        <f>'คะแนนดิบ'!X20</f>
+        <f>'คะแนนดิบ'!Y20</f>
         <v/>
       </c>
       <c r="K21" s="27">
@@ -1784,15 +1784,15 @@
         <v/>
       </c>
       <c r="F22" s="36">
-        <f>'คะแนนดิบ'!Q21</f>
+        <f>'คะแนนดิบ'!R21</f>
         <v/>
       </c>
       <c r="G22" s="35">
-        <f>ROUND((F22/130)*50, 2)</f>
+        <f>ROUND((F22/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H22" s="36">
-        <f>'คะแนนดิบ'!U21</f>
+        <f>'คะแนนดิบ'!V21</f>
         <v/>
       </c>
       <c r="I22" s="35">
@@ -1800,7 +1800,7 @@
         <v/>
       </c>
       <c r="J22" s="36">
-        <f>'คะแนนดิบ'!X21</f>
+        <f>'คะแนนดิบ'!Y21</f>
         <v/>
       </c>
       <c r="K22" s="35">
@@ -1842,15 +1842,15 @@
         <v/>
       </c>
       <c r="F23" s="28">
-        <f>'คะแนนดิบ'!Q22</f>
+        <f>'คะแนนดิบ'!R22</f>
         <v/>
       </c>
       <c r="G23" s="27">
-        <f>ROUND((F23/130)*50, 2)</f>
+        <f>ROUND((F23/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H23" s="28">
-        <f>'คะแนนดิบ'!U22</f>
+        <f>'คะแนนดิบ'!V22</f>
         <v/>
       </c>
       <c r="I23" s="27">
@@ -1858,7 +1858,7 @@
         <v/>
       </c>
       <c r="J23" s="28">
-        <f>'คะแนนดิบ'!X22</f>
+        <f>'คะแนนดิบ'!Y22</f>
         <v/>
       </c>
       <c r="K23" s="27">
@@ -1900,15 +1900,15 @@
         <v/>
       </c>
       <c r="F24" s="36">
-        <f>'คะแนนดิบ'!Q23</f>
+        <f>'คะแนนดิบ'!R23</f>
         <v/>
       </c>
       <c r="G24" s="35">
-        <f>ROUND((F24/130)*50, 2)</f>
+        <f>ROUND((F24/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H24" s="36">
-        <f>'คะแนนดิบ'!U23</f>
+        <f>'คะแนนดิบ'!V23</f>
         <v/>
       </c>
       <c r="I24" s="35">
@@ -1916,7 +1916,7 @@
         <v/>
       </c>
       <c r="J24" s="36">
-        <f>'คะแนนดิบ'!X23</f>
+        <f>'คะแนนดิบ'!Y23</f>
         <v/>
       </c>
       <c r="K24" s="35">
@@ -1958,15 +1958,15 @@
         <v/>
       </c>
       <c r="F25" s="28">
-        <f>'คะแนนดิบ'!Q24</f>
+        <f>'คะแนนดิบ'!R24</f>
         <v/>
       </c>
       <c r="G25" s="27">
-        <f>ROUND((F25/130)*50, 2)</f>
+        <f>ROUND((F25/150)*50, 2)</f>
         <v/>
       </c>
       <c r="H25" s="28">
-        <f>'คะแนนดิบ'!U24</f>
+        <f>'คะแนนดิบ'!V24</f>
         <v/>
       </c>
       <c r="I25" s="27">
@@ -1974,7 +1974,7 @@
         <v/>
       </c>
       <c r="J25" s="28">
-        <f>'คะแนนดิบ'!X24</f>
+        <f>'คะแนนดิบ'!Y24</f>
         <v/>
       </c>
       <c r="K25" s="27">
@@ -2354,7 +2354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2373,14 +2373,15 @@
     <col width="15" customWidth="1" min="14" max="14"/>
     <col width="15" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="15" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="15" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2408,7 +2409,7 @@
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>คะแนนเก็บตามภาระงาน (Assignment 1 - 13 | เต็ม 130 คะแนน)</t>
+          <t>คะแนนเก็บตามภาระงาน (Assignment 1 - 13 + คะแนนเก็บเพิ่ม | เต็ม 150 คะแนน)</t>
         </is>
       </c>
       <c r="E4" s="9" t="n"/>
@@ -2425,20 +2426,21 @@
       <c r="P4" s="9" t="n"/>
       <c r="Q4" s="9" t="n"/>
       <c r="R4" s="9" t="n"/>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="9" t="n"/>
+      <c r="T4" s="10" t="inlineStr">
         <is>
           <t>สอบกลางภาค (เต็ม 100 คะแนน)</t>
         </is>
       </c>
-      <c r="T4" s="11" t="n"/>
       <c r="U4" s="11" t="n"/>
-      <c r="V4" s="12" t="inlineStr">
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="12" t="inlineStr">
         <is>
           <t>สอบปลายภาค (เต็ม 100 คะแนน)</t>
         </is>
       </c>
-      <c r="W4" s="13" t="n"/>
       <c r="X4" s="13" t="n"/>
+      <c r="Y4" s="13" t="n"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -2547,49 +2549,55 @@
 (10)</t>
         </is>
       </c>
-      <c r="Q5" s="16" t="inlineStr">
+      <c r="Q5" s="18" t="inlineStr">
+        <is>
+          <t>คะแนนเก็บเพิ่ม
+(20)</t>
+        </is>
+      </c>
+      <c r="R5" s="16" t="inlineStr">
         <is>
           <t>รวมงาน
-(130)</t>
-        </is>
-      </c>
-      <c r="R5" s="16" t="inlineStr">
+(150)</t>
+        </is>
+      </c>
+      <c r="S5" s="16" t="inlineStr">
         <is>
           <t>ร้อยละ
 (%)</t>
         </is>
       </c>
-      <c r="S5" s="19" t="inlineStr">
+      <c r="T5" s="19" t="inlineStr">
         <is>
           <t>ข้อกา
 ปรนัย (40)</t>
         </is>
       </c>
-      <c r="T5" s="19" t="inlineStr">
+      <c r="U5" s="19" t="inlineStr">
         <is>
           <t>ข้อเขียน
 อัตนัย (60)</t>
         </is>
       </c>
-      <c r="U5" s="16" t="inlineStr">
+      <c r="V5" s="16" t="inlineStr">
         <is>
           <t>รวมกลางภาค
 (100)</t>
         </is>
       </c>
-      <c r="V5" s="20" t="inlineStr">
+      <c r="W5" s="20" t="inlineStr">
         <is>
           <t>ข้อกา
 ปรนัย (40)</t>
         </is>
       </c>
-      <c r="W5" s="20" t="inlineStr">
+      <c r="X5" s="20" t="inlineStr">
         <is>
           <t>ข้อเขียน
 อัตนัย (60)</t>
         </is>
       </c>
-      <c r="X5" s="16" t="inlineStr">
+      <c r="Y5" s="16" t="inlineStr">
         <is>
           <t>รวมปลายภาค
 (100)</t>
@@ -2649,32 +2657,35 @@
       <c r="P6" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Q6" s="50">
-        <f>SUM(D6:P6)</f>
-        <v/>
-      </c>
-      <c r="R6" s="27">
-        <f>ROUND((Q6/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S6" s="26" t="n">
-        <v>22</v>
+      <c r="Q6" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="R6" s="50">
+        <f>SUM(D6:Q6)</f>
+        <v/>
+      </c>
+      <c r="S6" s="27">
+        <f>ROUND((R6/150)*100, 2)</f>
+        <v/>
       </c>
       <c r="T6" s="26" t="n">
         <v>22</v>
       </c>
-      <c r="U6" s="50">
-        <f>SUM(S6:T6)</f>
-        <v/>
-      </c>
-      <c r="V6" s="26" t="n">
+      <c r="U6" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="V6" s="50">
+        <f>SUM(T6:U6)</f>
+        <v/>
+      </c>
+      <c r="W6" s="26" t="n">
         <v>24</v>
       </c>
-      <c r="W6" s="26" t="n">
+      <c r="X6" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="X6" s="50">
-        <f>SUM(V6:W6)</f>
+      <c r="Y6" s="50">
+        <f>SUM(W6:X6)</f>
         <v/>
       </c>
     </row>
@@ -2731,32 +2742,35 @@
       <c r="P7" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="52">
-        <f>SUM(D7:P7)</f>
-        <v/>
-      </c>
-      <c r="R7" s="35">
-        <f>ROUND((Q7/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S7" s="34" t="n">
+      <c r="Q7" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="52">
+        <f>SUM(D7:Q7)</f>
+        <v/>
+      </c>
+      <c r="S7" s="35">
+        <f>ROUND((R7/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T7" s="34" t="n">
         <v>17</v>
       </c>
-      <c r="T7" s="34" t="n">
+      <c r="U7" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="U7" s="52">
-        <f>SUM(S7:T7)</f>
-        <v/>
-      </c>
-      <c r="V7" s="34" t="n">
+      <c r="V7" s="52">
+        <f>SUM(T7:U7)</f>
+        <v/>
+      </c>
+      <c r="W7" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="W7" s="34" t="n">
+      <c r="X7" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="X7" s="52">
-        <f>SUM(V7:W7)</f>
+      <c r="Y7" s="52">
+        <f>SUM(W7:X7)</f>
         <v/>
       </c>
     </row>
@@ -2813,32 +2827,35 @@
       <c r="P8" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="50">
-        <f>SUM(D8:P8)</f>
-        <v/>
-      </c>
-      <c r="R8" s="27">
-        <f>ROUND((Q8/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S8" s="26" t="n">
+      <c r="Q8" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="R8" s="50">
+        <f>SUM(D8:Q8)</f>
+        <v/>
+      </c>
+      <c r="S8" s="27">
+        <f>ROUND((R8/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T8" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="T8" s="26" t="n">
+      <c r="U8" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="U8" s="50">
-        <f>SUM(S8:T8)</f>
-        <v/>
-      </c>
-      <c r="V8" s="26" t="n">
+      <c r="V8" s="50">
+        <f>SUM(T8:U8)</f>
+        <v/>
+      </c>
+      <c r="W8" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="W8" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="X8" s="50">
-        <f>SUM(V8:W8)</f>
+      <c r="X8" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="50">
+        <f>SUM(W8:X8)</f>
         <v/>
       </c>
     </row>
@@ -2895,32 +2912,35 @@
       <c r="P9" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="Q9" s="52">
-        <f>SUM(D9:P9)</f>
-        <v/>
-      </c>
-      <c r="R9" s="35">
-        <f>ROUND((Q9/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S9" s="34" t="n">
+      <c r="Q9" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="R9" s="52">
+        <f>SUM(D9:Q9)</f>
+        <v/>
+      </c>
+      <c r="S9" s="35">
+        <f>ROUND((R9/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T9" s="34" t="n">
         <v>27</v>
       </c>
-      <c r="T9" s="34" t="n">
+      <c r="U9" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="U9" s="52">
-        <f>SUM(S9:T9)</f>
-        <v/>
-      </c>
-      <c r="V9" s="34" t="n">
+      <c r="V9" s="52">
+        <f>SUM(T9:U9)</f>
+        <v/>
+      </c>
+      <c r="W9" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="W9" s="34" t="n">
+      <c r="X9" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="X9" s="52">
-        <f>SUM(V9:W9)</f>
+      <c r="Y9" s="52">
+        <f>SUM(W9:X9)</f>
         <v/>
       </c>
     </row>
@@ -2977,32 +2997,35 @@
       <c r="P10" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" s="50">
-        <f>SUM(D10:P10)</f>
-        <v/>
-      </c>
-      <c r="R10" s="27">
-        <f>ROUND((Q10/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S10" s="26" t="n">
+      <c r="Q10" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="R10" s="50">
+        <f>SUM(D10:Q10)</f>
+        <v/>
+      </c>
+      <c r="S10" s="27">
+        <f>ROUND((R10/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T10" s="26" t="n">
         <v>14</v>
       </c>
-      <c r="T10" s="26" t="n">
+      <c r="U10" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="U10" s="50">
-        <f>SUM(S10:T10)</f>
-        <v/>
-      </c>
-      <c r="V10" s="26" t="n">
+      <c r="V10" s="50">
+        <f>SUM(T10:U10)</f>
+        <v/>
+      </c>
+      <c r="W10" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="W10" s="26" t="n">
+      <c r="X10" s="26" t="n">
         <v>18</v>
       </c>
-      <c r="X10" s="50">
-        <f>SUM(V10:W10)</f>
+      <c r="Y10" s="50">
+        <f>SUM(W10:X10)</f>
         <v/>
       </c>
     </row>
@@ -3059,32 +3082,35 @@
       <c r="P11" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="Q11" s="52">
-        <f>SUM(D11:P11)</f>
-        <v/>
-      </c>
-      <c r="R11" s="35">
-        <f>ROUND((Q11/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S11" s="34" t="n">
+      <c r="Q11" s="34" t="n">
         <v>18</v>
       </c>
+      <c r="R11" s="52">
+        <f>SUM(D11:Q11)</f>
+        <v/>
+      </c>
+      <c r="S11" s="35">
+        <f>ROUND((R11/150)*100, 2)</f>
+        <v/>
+      </c>
       <c r="T11" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="U11" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="U11" s="52">
-        <f>SUM(S11:T11)</f>
-        <v/>
-      </c>
-      <c r="V11" s="34" t="n">
+      <c r="V11" s="52">
+        <f>SUM(T11:U11)</f>
+        <v/>
+      </c>
+      <c r="W11" s="34" t="n">
         <v>17</v>
       </c>
-      <c r="W11" s="34" t="n">
+      <c r="X11" s="34" t="n">
         <v>33</v>
       </c>
-      <c r="X11" s="52">
-        <f>SUM(V11:W11)</f>
+      <c r="Y11" s="52">
+        <f>SUM(W11:X11)</f>
         <v/>
       </c>
     </row>
@@ -3141,32 +3167,35 @@
       <c r="P12" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="50">
-        <f>SUM(D12:P12)</f>
-        <v/>
-      </c>
-      <c r="R12" s="27">
-        <f>ROUND((Q12/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S12" s="26" t="n">
+      <c r="Q12" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="R12" s="50">
+        <f>SUM(D12:Q12)</f>
+        <v/>
+      </c>
+      <c r="S12" s="27">
+        <f>ROUND((R12/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T12" s="26" t="n">
         <v>24</v>
       </c>
-      <c r="T12" s="26" t="n">
+      <c r="U12" s="26" t="n">
         <v>28</v>
       </c>
-      <c r="U12" s="50">
-        <f>SUM(S12:T12)</f>
-        <v/>
-      </c>
-      <c r="V12" s="26" t="n">
+      <c r="V12" s="50">
+        <f>SUM(T12:U12)</f>
+        <v/>
+      </c>
+      <c r="W12" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="W12" s="26" t="n">
+      <c r="X12" s="26" t="n">
         <v>25</v>
       </c>
-      <c r="X12" s="50">
-        <f>SUM(V12:W12)</f>
+      <c r="Y12" s="50">
+        <f>SUM(W12:X12)</f>
         <v/>
       </c>
     </row>
@@ -3223,32 +3252,35 @@
       <c r="P13" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="Q13" s="52">
-        <f>SUM(D13:P13)</f>
-        <v/>
-      </c>
-      <c r="R13" s="35">
-        <f>ROUND((Q13/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S13" s="34" t="n">
+      <c r="Q13" s="34" t="n">
         <v>17</v>
       </c>
+      <c r="R13" s="52">
+        <f>SUM(D13:Q13)</f>
+        <v/>
+      </c>
+      <c r="S13" s="35">
+        <f>ROUND((R13/150)*100, 2)</f>
+        <v/>
+      </c>
       <c r="T13" s="34" t="n">
+        <v>17</v>
+      </c>
+      <c r="U13" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="U13" s="52">
-        <f>SUM(S13:T13)</f>
-        <v/>
-      </c>
-      <c r="V13" s="34" t="n">
+      <c r="V13" s="52">
+        <f>SUM(T13:U13)</f>
+        <v/>
+      </c>
+      <c r="W13" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="W13" s="34" t="n">
+      <c r="X13" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="X13" s="52">
-        <f>SUM(V13:W13)</f>
+      <c r="Y13" s="52">
+        <f>SUM(W13:X13)</f>
         <v/>
       </c>
     </row>
@@ -3305,32 +3337,35 @@
       <c r="P14" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="50">
-        <f>SUM(D14:P14)</f>
-        <v/>
-      </c>
-      <c r="R14" s="27">
-        <f>ROUND((Q14/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S14" s="26" t="n">
-        <v>10</v>
+      <c r="Q14" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="R14" s="50">
+        <f>SUM(D14:Q14)</f>
+        <v/>
+      </c>
+      <c r="S14" s="27">
+        <f>ROUND((R14/150)*100, 2)</f>
+        <v/>
       </c>
       <c r="T14" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="U14" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="U14" s="50">
-        <f>SUM(S14:T14)</f>
-        <v/>
-      </c>
-      <c r="V14" s="26" t="n">
+      <c r="V14" s="50">
+        <f>SUM(T14:U14)</f>
+        <v/>
+      </c>
+      <c r="W14" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="W14" s="26" t="n">
+      <c r="X14" s="26" t="n">
         <v>22</v>
       </c>
-      <c r="X14" s="50">
-        <f>SUM(V14:W14)</f>
+      <c r="Y14" s="50">
+        <f>SUM(W14:X14)</f>
         <v/>
       </c>
     </row>
@@ -3387,32 +3422,35 @@
       <c r="P15" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="52">
-        <f>SUM(D15:P15)</f>
-        <v/>
-      </c>
-      <c r="R15" s="35">
-        <f>ROUND((Q15/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S15" s="34" t="n">
+      <c r="Q15" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="52">
+        <f>SUM(D15:Q15)</f>
+        <v/>
+      </c>
+      <c r="S15" s="35">
+        <f>ROUND((R15/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T15" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="T15" s="34" t="n">
+      <c r="U15" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="U15" s="52">
-        <f>SUM(S15:T15)</f>
-        <v/>
-      </c>
-      <c r="V15" s="34" t="n">
+      <c r="V15" s="52">
+        <f>SUM(T15:U15)</f>
+        <v/>
+      </c>
+      <c r="W15" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="W15" s="34" t="n">
+      <c r="X15" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="X15" s="52">
-        <f>SUM(V15:W15)</f>
+      <c r="Y15" s="52">
+        <f>SUM(W15:X15)</f>
         <v/>
       </c>
     </row>
@@ -3469,32 +3507,35 @@
       <c r="P16" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="50">
-        <f>SUM(D16:P16)</f>
-        <v/>
-      </c>
-      <c r="R16" s="27">
-        <f>ROUND((Q16/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S16" s="26" t="n">
+      <c r="Q16" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="R16" s="50">
+        <f>SUM(D16:Q16)</f>
+        <v/>
+      </c>
+      <c r="S16" s="27">
+        <f>ROUND((R16/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T16" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="T16" s="26" t="n">
-        <v>10</v>
-      </c>
-      <c r="U16" s="50">
-        <f>SUM(S16:T16)</f>
-        <v/>
-      </c>
-      <c r="V16" s="26" t="n">
+      <c r="U16" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="V16" s="50">
+        <f>SUM(T16:U16)</f>
+        <v/>
+      </c>
+      <c r="W16" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="W16" s="26" t="n">
+      <c r="X16" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="X16" s="50">
-        <f>SUM(V16:W16)</f>
+      <c r="Y16" s="50">
+        <f>SUM(W16:X16)</f>
         <v/>
       </c>
     </row>
@@ -3551,32 +3592,35 @@
       <c r="P17" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" s="52">
-        <f>SUM(D17:P17)</f>
-        <v/>
-      </c>
-      <c r="R17" s="35">
-        <f>ROUND((Q17/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S17" s="34" t="n">
+      <c r="Q17" s="34" t="n">
         <v>20</v>
       </c>
+      <c r="R17" s="52">
+        <f>SUM(D17:Q17)</f>
+        <v/>
+      </c>
+      <c r="S17" s="35">
+        <f>ROUND((R17/150)*100, 2)</f>
+        <v/>
+      </c>
       <c r="T17" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="U17" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="U17" s="52">
-        <f>SUM(S17:T17)</f>
-        <v/>
-      </c>
-      <c r="V17" s="34" t="n">
+      <c r="V17" s="52">
+        <f>SUM(T17:U17)</f>
+        <v/>
+      </c>
+      <c r="W17" s="34" t="n">
         <v>17</v>
       </c>
-      <c r="W17" s="34" t="n">
+      <c r="X17" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="X17" s="52">
-        <f>SUM(V17:W17)</f>
+      <c r="Y17" s="52">
+        <f>SUM(W17:X17)</f>
         <v/>
       </c>
     </row>
@@ -3633,32 +3677,35 @@
       <c r="P18" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="50">
-        <f>SUM(D18:P18)</f>
-        <v/>
-      </c>
-      <c r="R18" s="27">
-        <f>ROUND((Q18/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S18" s="26" t="n">
+      <c r="Q18" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="R18" s="50">
+        <f>SUM(D18:Q18)</f>
+        <v/>
+      </c>
+      <c r="S18" s="27">
+        <f>ROUND((R18/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T18" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="T18" s="26" t="n">
+      <c r="U18" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="U18" s="50">
-        <f>SUM(S18:T18)</f>
-        <v/>
-      </c>
-      <c r="V18" s="26" t="n">
+      <c r="V18" s="50">
+        <f>SUM(T18:U18)</f>
+        <v/>
+      </c>
+      <c r="W18" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="W18" s="26" t="n">
+      <c r="X18" s="26" t="n">
         <v>23</v>
       </c>
-      <c r="X18" s="50">
-        <f>SUM(V18:W18)</f>
+      <c r="Y18" s="50">
+        <f>SUM(W18:X18)</f>
         <v/>
       </c>
     </row>
@@ -3715,32 +3762,35 @@
       <c r="P19" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="Q19" s="52">
-        <f>SUM(D19:P19)</f>
-        <v/>
-      </c>
-      <c r="R19" s="35">
-        <f>ROUND((Q19/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S19" s="34" t="n">
+      <c r="Q19" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="R19" s="52">
+        <f>SUM(D19:Q19)</f>
+        <v/>
+      </c>
+      <c r="S19" s="35">
+        <f>ROUND((R19/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T19" s="34" t="n">
         <v>22</v>
       </c>
-      <c r="T19" s="34" t="n">
+      <c r="U19" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="U19" s="52">
-        <f>SUM(S19:T19)</f>
-        <v/>
-      </c>
-      <c r="V19" s="34" t="n">
+      <c r="V19" s="52">
+        <f>SUM(T19:U19)</f>
+        <v/>
+      </c>
+      <c r="W19" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="W19" s="34" t="n">
+      <c r="X19" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="X19" s="52">
-        <f>SUM(V19:W19)</f>
+      <c r="Y19" s="52">
+        <f>SUM(W19:X19)</f>
         <v/>
       </c>
     </row>
@@ -3797,32 +3847,35 @@
       <c r="P20" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="Q20" s="50">
-        <f>SUM(D20:P20)</f>
-        <v/>
-      </c>
-      <c r="R20" s="27">
-        <f>ROUND((Q20/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S20" s="26" t="n">
+      <c r="Q20" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="R20" s="50">
+        <f>SUM(D20:Q20)</f>
+        <v/>
+      </c>
+      <c r="S20" s="27">
+        <f>ROUND((R20/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T20" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="T20" s="26" t="n">
+      <c r="U20" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="U20" s="50">
-        <f>SUM(S20:T20)</f>
-        <v/>
-      </c>
-      <c r="V20" s="26" t="n">
+      <c r="V20" s="50">
+        <f>SUM(T20:U20)</f>
+        <v/>
+      </c>
+      <c r="W20" s="26" t="n">
         <v>14</v>
       </c>
-      <c r="W20" s="26" t="n">
+      <c r="X20" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="X20" s="50">
-        <f>SUM(V20:W20)</f>
+      <c r="Y20" s="50">
+        <f>SUM(W20:X20)</f>
         <v/>
       </c>
     </row>
@@ -3879,32 +3932,35 @@
       <c r="P21" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="52">
-        <f>SUM(D21:P21)</f>
-        <v/>
-      </c>
-      <c r="R21" s="35">
-        <f>ROUND((Q21/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S21" s="34" t="n">
+      <c r="Q21" s="34" t="n">
+        <v>20</v>
+      </c>
+      <c r="R21" s="52">
+        <f>SUM(D21:Q21)</f>
+        <v/>
+      </c>
+      <c r="S21" s="35">
+        <f>ROUND((R21/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T21" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="T21" s="34" t="n">
+      <c r="U21" s="34" t="n">
         <v>17</v>
       </c>
-      <c r="U21" s="52">
-        <f>SUM(S21:T21)</f>
-        <v/>
-      </c>
-      <c r="V21" s="34" t="n">
+      <c r="V21" s="52">
+        <f>SUM(T21:U21)</f>
+        <v/>
+      </c>
+      <c r="W21" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="W21" s="34" t="n">
+      <c r="X21" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="X21" s="52">
-        <f>SUM(V21:W21)</f>
+      <c r="Y21" s="52">
+        <f>SUM(W21:X21)</f>
         <v/>
       </c>
     </row>
@@ -3961,32 +4017,35 @@
       <c r="P22" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="50">
-        <f>SUM(D22:P22)</f>
-        <v/>
-      </c>
-      <c r="R22" s="27">
-        <f>ROUND((Q22/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S22" s="26" t="n">
+      <c r="Q22" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="R22" s="50">
+        <f>SUM(D22:Q22)</f>
+        <v/>
+      </c>
+      <c r="S22" s="27">
+        <f>ROUND((R22/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T22" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="T22" s="26" t="n">
+      <c r="U22" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="U22" s="50">
-        <f>SUM(S22:T22)</f>
-        <v/>
-      </c>
-      <c r="V22" s="26" t="n">
+      <c r="V22" s="50">
+        <f>SUM(T22:U22)</f>
+        <v/>
+      </c>
+      <c r="W22" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="W22" s="53" t="n">
+      <c r="X22" s="53" t="n">
         <v>23.5</v>
       </c>
-      <c r="X22" s="50">
-        <f>SUM(V22:W22)</f>
+      <c r="Y22" s="50">
+        <f>SUM(W22:X22)</f>
         <v/>
       </c>
     </row>
@@ -4043,32 +4102,35 @@
       <c r="P23" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="52">
-        <f>SUM(D23:P23)</f>
-        <v/>
-      </c>
-      <c r="R23" s="35">
-        <f>ROUND((Q23/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S23" s="34" t="n">
+      <c r="Q23" s="34" t="n">
         <v>18</v>
       </c>
+      <c r="R23" s="52">
+        <f>SUM(D23:Q23)</f>
+        <v/>
+      </c>
+      <c r="S23" s="35">
+        <f>ROUND((R23/150)*100, 2)</f>
+        <v/>
+      </c>
       <c r="T23" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="U23" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="U23" s="52">
-        <f>SUM(S23:T23)</f>
-        <v/>
-      </c>
-      <c r="V23" s="34" t="n">
+      <c r="V23" s="52">
+        <f>SUM(T23:U23)</f>
+        <v/>
+      </c>
+      <c r="W23" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="W23" s="34" t="n">
+      <c r="X23" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="X23" s="52">
-        <f>SUM(V23:W23)</f>
+      <c r="Y23" s="52">
+        <f>SUM(W23:X23)</f>
         <v/>
       </c>
     </row>
@@ -4125,32 +4187,35 @@
       <c r="P24" s="51" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" s="50">
-        <f>SUM(D24:P24)</f>
-        <v/>
-      </c>
-      <c r="R24" s="27">
-        <f>ROUND((Q24/130)*100, 2)</f>
-        <v/>
-      </c>
-      <c r="S24" s="26" t="n">
+      <c r="Q24" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="R24" s="50">
+        <f>SUM(D24:Q24)</f>
+        <v/>
+      </c>
+      <c r="S24" s="27">
+        <f>ROUND((R24/150)*100, 2)</f>
+        <v/>
+      </c>
+      <c r="T24" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="T24" s="26" t="n">
+      <c r="U24" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="U24" s="50">
-        <f>SUM(S24:T24)</f>
-        <v/>
-      </c>
-      <c r="V24" s="26" t="n">
+      <c r="V24" s="50">
+        <f>SUM(T24:U24)</f>
+        <v/>
+      </c>
+      <c r="W24" s="26" t="n">
         <v>21</v>
       </c>
-      <c r="W24" s="26" t="n">
+      <c r="X24" s="26" t="n">
         <v>18</v>
       </c>
-      <c r="X24" s="50">
-        <f>SUM(V24:W24)</f>
+      <c r="Y24" s="50">
+        <f>SUM(W24:X24)</f>
         <v/>
       </c>
     </row>
@@ -4214,7 +4279,7 @@
         <f>AVERAGE(P6:P24)</f>
         <v/>
       </c>
-      <c r="Q25" s="41">
+      <c r="Q25" s="54">
         <f>AVERAGE(Q6:Q24)</f>
         <v/>
       </c>
@@ -4222,7 +4287,7 @@
         <f>AVERAGE(R6:R24)</f>
         <v/>
       </c>
-      <c r="S25" s="54">
+      <c r="S25" s="41">
         <f>AVERAGE(S6:S24)</f>
         <v/>
       </c>
@@ -4230,11 +4295,11 @@
         <f>AVERAGE(T6:T24)</f>
         <v/>
       </c>
-      <c r="U25" s="41">
+      <c r="U25" s="54">
         <f>AVERAGE(U6:U24)</f>
         <v/>
       </c>
-      <c r="V25" s="54">
+      <c r="V25" s="41">
         <f>AVERAGE(V6:V24)</f>
         <v/>
       </c>
@@ -4242,8 +4307,12 @@
         <f>AVERAGE(W6:W24)</f>
         <v/>
       </c>
-      <c r="X25" s="41">
+      <c r="X25" s="54">
         <f>AVERAGE(X6:X24)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="41">
+        <f>AVERAGE(Y6:Y24)</f>
         <v/>
       </c>
     </row>
@@ -4307,15 +4376,15 @@
         <f>MAX(P6:P24)</f>
         <v/>
       </c>
-      <c r="Q26" s="56">
+      <c r="Q26" s="55">
         <f>MAX(Q6:Q24)</f>
         <v/>
       </c>
-      <c r="R26" s="41">
+      <c r="R26" s="56">
         <f>MAX(R6:R24)</f>
         <v/>
       </c>
-      <c r="S26" s="55">
+      <c r="S26" s="41">
         <f>MAX(S6:S24)</f>
         <v/>
       </c>
@@ -4323,11 +4392,11 @@
         <f>MAX(T6:T24)</f>
         <v/>
       </c>
-      <c r="U26" s="56">
+      <c r="U26" s="55">
         <f>MAX(U6:U24)</f>
         <v/>
       </c>
-      <c r="V26" s="55">
+      <c r="V26" s="56">
         <f>MAX(V6:V24)</f>
         <v/>
       </c>
@@ -4335,8 +4404,12 @@
         <f>MAX(W6:W24)</f>
         <v/>
       </c>
-      <c r="X26" s="56">
+      <c r="X26" s="55">
         <f>MAX(X6:X24)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="56">
+        <f>MAX(Y6:Y24)</f>
         <v/>
       </c>
     </row>
@@ -4400,15 +4473,15 @@
         <f>MIN(P6:P24)</f>
         <v/>
       </c>
-      <c r="Q27" s="58">
+      <c r="Q27" s="57">
         <f>MIN(Q6:Q24)</f>
         <v/>
       </c>
-      <c r="R27" s="46">
+      <c r="R27" s="58">
         <f>MIN(R6:R24)</f>
         <v/>
       </c>
-      <c r="S27" s="57">
+      <c r="S27" s="46">
         <f>MIN(S6:S24)</f>
         <v/>
       </c>
@@ -4416,11 +4489,11 @@
         <f>MIN(T6:T24)</f>
         <v/>
       </c>
-      <c r="U27" s="58">
+      <c r="U27" s="57">
         <f>MIN(U6:U24)</f>
         <v/>
       </c>
-      <c r="V27" s="57">
+      <c r="V27" s="58">
         <f>MIN(V6:V24)</f>
         <v/>
       </c>
@@ -4428,20 +4501,24 @@
         <f>MIN(W6:W24)</f>
         <v/>
       </c>
-      <c r="X27" s="58">
+      <c r="X27" s="57">
         <f>MIN(X6:X24)</f>
+        <v/>
+      </c>
+      <c r="Y27" s="58">
+        <f>MIN(Y6:Y24)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A2:X2"/>
-    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="D4:S4"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="T4:V4"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="D4:R4"/>
-    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="W4:Y4"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A26:C26"/>
   </mergeCells>
